--- a/audiobooks.xlsx
+++ b/audiobooks.xlsx
@@ -749,7 +749,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2020</t>
+          <t>08/09/2020</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,27 +762,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
+          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chris Voss, Tahl Raz</t>
+          <t>Jocko Willink, Leif Babin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Harper Business</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17/05/2016</t>
+          <t>20/10/2015</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -795,27 +795,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Extreme Ownership: How U.S. Navy SEALs Lead and Win</t>
+          <t>How To Win Friends And Influence People</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jocko Willink, Leif Babin</t>
+          <t>Dale Carnegie</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20/10/2015</t>
+          <t>01/10/1936</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -828,12 +828,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Speak Like a CEO: How to Speak with Power, Lead with Clarity, and Command Any Room Without Saying a Word Too Much</t>
+          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CALDER MP KNOX</t>
+          <t>Nathan Soren</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>How to Talk to Anyone and Be More Charismatic: Improve Communication &amp; People Skills, Master Small Talk, Build Confidence &amp; Influence, Overcome Social Anxiety, and Make Friends in Any Conversation</t>
+          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Stephen R. Covey, Sean Covey</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nathan Soren</t>
+          <t>Free Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/01/1989</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -881,27 +881,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
+          <t>Never Split the Difference: Unlock Your Persuasion Potential in Professional and Personal Life</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Guidara</t>
+          <t>Chris Voss, Tahl Raz</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Optimism Press</t>
+          <t>Harper Business</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25/10/2022</t>
+          <t>17/05/2016</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -914,27 +914,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The 7 Habits of Highly Effective People: 30th Anniversary Edition</t>
+          <t>Unreasonable Hospitality: The Remarkable Power of Giving People More Than They Expect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Stephen R. Covey, Sean Covey</t>
+          <t>Will Guidara</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Free Press</t>
+          <t>Optimism Press</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>01/01/1989</t>
+          <t>25/10/2022</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -947,31 +947,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Think and Grow Rich</t>
+          <t>The Art of War</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mitch Horowitz, Napoleon Hill, Theresa Puskar</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>The Ralston Society</t>
+          <t>Sun Tzu</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>01/01/1937</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,7 +977,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Ralston Society</t>
+          <t>Mindpower Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1000,7 +987,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/03/1937</t>
+          <t>01/04/2015</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1013,31 +1000,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Las 32 leyes inquebrantables del dinero y el éxito: Transforma tu vida y libera tu potencial</t>
+          <t>The Art of Fighting: The Transformative Power of Conflict</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brian Tracy</t>
+          <t>Priya Parker</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Reverté Management</t>
+          <t>Riverhead Books</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>08/09/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1106,27 +1090,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>This Is Me: A Reckoning</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
+          <t>Hayden Panettiere</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>Grand Central Publishing</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1120,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I'm Glad My Mom Died</t>
+          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jennette McCurdy</t>
+          <t>Anthony Bourdain, Irvine Welsh</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>09/08/2022</t>
+          <t>01/08/2000</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1169,28 +1153,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stripped Down: Unfiltered and Unapologetic</t>
+          <t>I'm Glad My Mom Died</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bunnie Xo</t>
+          <t>Jennette McCurdy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>HarperCollins Publishers</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
-        </is>
+          <t>09/08/2022</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1199,31 +1186,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kitchen Confidential: Adventures in the Culinary Underbelly</t>
+          <t>Strangers: A Memoir of Marriage</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anthony Bourdain, Irvine Welsh</t>
+          <t>Belle Burden</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>The Dial Press</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/01/2000</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>13/01/2026</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1232,27 +1216,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dogs, Boys, and Other Things I’ve Cried About: A Memoir</t>
+          <t>Roll the Calls: A Memoir</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Isabel Klee</t>
+          <t>Ari Emanuel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>William Morrow</t>
+          <t>Alfred A. Knopf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
@@ -1262,27 +1246,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Make-Believe: A Memoir of Magic and Madness</t>
+          <t>The Steps: A Memoir</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hannah Murray</t>
+          <t>Sylvester Stallone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Dial Press</t>
+          <t>William Morrow</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
     </row>
@@ -1292,28 +1276,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>This Is Me: A Reckoning</t>
+          <t>Poems &amp; Prayers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hayden Panettiere</t>
+          <t>Matthew McConaughey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Grand Central Publishing</t>
+          <t>Crown Publishing Group</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
-        </is>
+          <t>16/09/2025</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1322,28 +1309,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>In the Days of My Youth I Was Told What It Means to Be a Man: A Memoir</t>
+          <t>Told You So</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tom Junod</t>
+          <t>Mayci Neeley</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Doubleday</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
-        </is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1352,31 +1342,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Going There (read by Katie Couric)</t>
+          <t>Stripped Down: Unfiltered and Unapologetic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Katie Couric</t>
+          <t>Bunnie Xo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Dey Street Books</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26/10/2021</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>17/02/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1385,28 +1372,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>You with the Sad Eyes: A Memoir</t>
+          <t>Fear and Loathing in Las Vegas: A Savage Journey to the Heart of the American Dream</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Christina Applegate</t>
+          <t>Hunter S. Thompson</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Random House</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>03/03/2026</t>
-        </is>
+          <t>07/07/1972</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1475,27 +1465,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>A Court of Thorns and Roses</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29/07/1954</t>
+          <t>05/05/2015</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1508,27 +1498,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fourth Wing</t>
+          <t>A Court of Mist and Fury</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Red Tower Books</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>02/05/2023</t>
+          <t>03/05/2016</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,27 +1531,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Fourth Wing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Del Rey Books</t>
+          <t>Red Tower Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
+          <t>02/05/2023</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1574,27 +1564,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>George R. R. Martin</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bantam Spectra</t>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/08/1996</t>
+          <t>29/07/1954</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1607,7 +1597,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Throne of Glass</t>
+          <t>A Court of Wings and Ruin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1627,7 +1617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/08/2012</t>
+          <t>02/05/2017</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1640,7 +1630,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A Court of Wings and Ruin</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1650,7 +1640,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Bloomsbury YA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1660,7 +1650,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/05/2017</t>
+          <t>02/08/2012</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1673,27 +1663,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Iron Flame</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rebecca Yarros</t>
+          <t>Pierce Brown</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Red Tower Books (Entangled Publishing)</t>
+          <t>Del Rey Books</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>07/11/2023</t>
+          <t>28/01/2014</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1716,7 +1706,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bloomsbury YA</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1739,30 +1729,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Crown of Midnight</t>
+          <t>Iron Flame</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Rebecca Yarros</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Red Tower Books (Entangled Publishing)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>07/11/2023</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>House of Earth and Blood (1 of 2) [Dramatized Adaptation]: Crescent City 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Sarah J. Maas</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bloomsbury USA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bloomsbury Publishing</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Bloomsbury</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>27/08/2013</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>03/03/2020</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1842,7 +1865,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Pck</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1852,10 +1875,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>25/01/2025</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1896,32 +1921,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
+          <t>Regulate Your F*cking Nervous System: The No-Nonsense Guide to Understanding Why Your Body Won't Calm Down (And How to Finally Fix It)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mark Manson</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>HarperOne</t>
-        </is>
-      </c>
+          <t>Marieme Seck</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13/09/2016</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
+          <t>17/09/2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1929,22 +1948,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Regulate Your F*cking Nervous System: The No-Nonsense Guide to Understanding Why Your Body Won't Calm Down (And How to Finally Fix It)</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Mark Manson</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>HarperOne</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+          <t>HarperCollins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>13/09/2016</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1952,29 +1981,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
+          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sabrina Alexis Bendory</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Thought Catalog Books</t>
-        </is>
-      </c>
+          <t>Brianna Wiest</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>09/09/2025</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1983,32 +2004,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mastering Conversation Skills Goodbye Awkwardness. Learn to Master the Art of Conversation and Become A Great Communicator, Even if You've Always Been Shy or Hate Small Talk</t>
+          <t>F*ck Failure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Helen Stone</t>
+          <t>benny blanco</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Author's Republic</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31/03/2020</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2016,12 +2035,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Mountain is You: Transforming Self-Sabotage Into Self-Mastery</t>
+          <t>Detached: How to Let Go, Heal, and Become Irresistible</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brianna Wiest</t>
+          <t>Sabrina Alexis Bendory</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2036,7 +2055,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/05/2020</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2049,17 +2068,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sex So Great She Can't Get Enough</t>
+          <t>The Power of Now</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Barbara Keesling PhD</t>
+          <t>Eckhart Tolle</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M. Evans &amp; Company</t>
+          <t>Namaste Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2069,7 +2088,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/2005</t>
+          <t>01/01/1997</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2082,27 +2101,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stop Letting Everything Affect You: How to break free from overthinking, emotional chaos and self-sabotage</t>
+          <t>Awaken the Giant Within, Updated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Daniel Chidiac</t>
+          <t>Tony Robbins</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Undercover Publishing House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>01/11/1991</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2115,17 +2134,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Power of Now</t>
+          <t>The Power of Feminine Energy: Becoming High-Value &amp; Feminine: Mastering Energy, Boundaries &amp; Hypergamy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eckhart Tolle</t>
+          <t>Amelia Vazquez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Namaste Publishing</t>
+          <t>Anna Milton</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2135,12 +2154,10 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/1997</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
+          <t>22/11/2025</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2153,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2208,28 +2225,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yesteryear: A GMA Book Club Pick: A Novel</t>
+          <t>Harry Potter and the Sorcerer's Stone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Caro Claire Burke</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Scholastic Corporation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>01/09/1998</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2238,17 +2258,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Harry Potter and the Sorcerer's Stone</t>
+          <t>The Calamity Club: A Novel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Kathryn Stockett</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Scholastic</t>
+          <t>Spiegel &amp; Grau</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2258,11 +2278,8 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/09/1998</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
+          <t>05/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2271,27 +2288,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Calamity Club: A Novel</t>
+          <t>Yesteryear: A GMA Book Club Pick: A Novel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kathryn Stockett</t>
+          <t>Caro Claire Burke</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Spiegel &amp; Grau</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
     </row>
@@ -2301,17 +2318,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Famesick: A Memoir</t>
+          <t>The Love Hypothesis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lena Dunham</t>
+          <t>Ali Hazelwood</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random House</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2321,8 +2338,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
-        </is>
+          <t>14/09/2021</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2331,17 +2351,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
+          <t>Theo of Golden: A Novel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Marieme Seck</t>
+          <t>Allen Levi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2351,8 +2371,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
-        </is>
+          <t>01/01/2023</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2361,28 +2384,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Theo of Golden: A Novel</t>
+          <t>Not giving a F*ck Anymore.: Stop People-Pleasing, Set Boundaries, and Start Living on Your Own Terms.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allen Levi</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Pck</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
-        </is>
+          <t>25/01/2025</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2391,17 +2417,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cancel Me If You Can</t>
+          <t>Protocols: An Operating Manual for the Human Body</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dave Portnoy</t>
+          <t>Andrew Huberman</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>S&amp;S/Simon Element</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2411,7 +2437,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
     </row>
@@ -2421,27 +2447,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harry Potter and the Chamber of Secrets</t>
+          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>James Clear</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Avery Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>02/07/1998</t>
+          <t>16/10/2018</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2454,31 +2480,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zando - Slowburn</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06/08/2024</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>21/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -2487,27 +2510,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Antonios Damilas</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/01/1488</t>
+          <t>02/07/1998</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2553,31 +2576,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atomic Habits: An Easy &amp; Proven Way to Build Good Habits &amp; Break Bad Ones</t>
+          <t>Regulate Your F*cking Nervous System: The No-Nonsense Guide to Understanding Why Your Body Won't Calm Down (And How to Finally Fix It)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>James Clear</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Avery Publishing</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>16/10/2018</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
+          <t>17/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2586,28 +2601,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regime Change: Inside the Imperial Presidency of Donald Trump</t>
+          <t>Harry Potter and the Prisoner of Azkaban</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maggie Haberman, Jonathan Swan</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
+          <t>08/07/1999</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -2616,27 +2634,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Fellowship of the Ring</t>
+          <t>The 48 Laws of Power</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>J.R.R. Tolkien</t>
+          <t>Robert Greene</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>George Allen &amp; Unwin</t>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29/07/1954</t>
+          <t>01/01/1998</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2649,31 +2667,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>This Is Me: A Reckoning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>Hayden Panettiere</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Antonios Damilas</t>
+          <t>Grand Central Publishing</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01/01/1488</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
+          <t>19/05/2026</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -2682,27 +2697,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Strangers: A Memoir of Marriage</t>
+          <t>Harry Potter and the Goblet of Fire</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Belle Burden</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Dial Press</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>13/01/2026</t>
+          <t>Independent</t>
         </is>
       </c>
     </row>
@@ -2712,27 +2717,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Poisoned Pen Press</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Independent</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -2742,28 +2737,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>A Court of Mist and Fury</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
-        </is>
+          <t>03/05/2016</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2805,27 +2803,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The 48 Laws of Power</t>
+          <t>The Fellowship of the Ring</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Robert Greene</t>
+          <t>J.R.R. Tolkien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Viking Press</t>
+          <t>George Allen &amp; Unwin</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01/01/1998</t>
+          <t>29/07/1954</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2838,7 +2836,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A Court of Mist and Fury</t>
+          <t>A Court of Wings and Ruin</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2858,7 +2856,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>03/05/2016</t>
+          <t>02/05/2017</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2871,28 +2869,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Whistler: A Novel</t>
+          <t>East of Eden</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Patchett</t>
+          <t>John Steinbeck</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Viking Press</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
-        </is>
+          <t>19/09/1952</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2901,17 +2902,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Red Rising</t>
+          <t>Famesick: A Memoir</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pierce Brown</t>
+          <t>Lena Dunham</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Del Rey Books</t>
+          <t>Random House</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2921,11 +2922,8 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>28/01/2014</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
+          <t>14/04/2026</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -2934,27 +2932,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Remarkably Bright Creatures: A Read with Jenna Pick</t>
+          <t>Throne of Glass</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shelby Van Pelt</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ecco Press</t>
+          <t>Bloomsbury YA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>03/05/2022</t>
+          <t>02/08/2012</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -2967,28 +2965,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Shampoo Effect: A Read with Jenna Pick: A Novel</t>
+          <t>The Subtle Art of Not Giving a F*ck: A Counterintuitive Approach to Living a Good Life</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jenny Jackson</t>
+          <t>Mark Manson</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Pamela Dorman Books</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
-        </is>
+          <t>13/09/2016</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2997,17 +2998,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
+          <t>Red Rising</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brooke Averick</t>
+          <t>Pierce Brown</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>Del Rey Books</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3017,8 +3018,11 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
-        </is>
+          <t>28/01/2014</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3027,31 +3031,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Correspondent: A Novel</t>
+          <t>Whistler: A Novel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Virginia Evans</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Crown Publishing Group</t>
+          <t>Ann Patchett</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>29/04/2025</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -3060,27 +3051,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Biological War: A Scenario</t>
+          <t>Fruit Fly</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Annie Jacobsen</t>
+          <t>Josh Silver</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dutton</t>
+          <t>Crooked Lane Books</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3090,61 +3081,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>My Husband's Wife: A Novel</t>
+          <t>The Divorce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alice Feeney</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Flatiron Books</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>A Game of Thrones: A Song of Ice and Fire: Book One</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>George R. R. Martin</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Bantam Spectra</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>01/08/1996</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
+          <t>26/05/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3213,27 +3171,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lights Out: An Into Darkness Novel</t>
+          <t>The Love Hypothesis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Ali Hazelwood</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zando - Slowburn</t>
+          <t>Berkley Books</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06/08/2024</t>
+          <t>14/09/2021</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3246,28 +3204,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phoebe Berman's Gonna Lose It: A Novel</t>
+          <t>Lights Out: An Into Darkness Novel</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Brooke Averick</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>Slowburn</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
-        </is>
+          <t>06/08/2024</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3276,28 +3237,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dolly All the Time: A GMA Book Club Pick</t>
+          <t>Fourth Wing (1 of 2) [Dramatized Adaptation]: The Empyrean 1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Annabel Monaghan</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>G.P. Putnam's Sons</t>
+          <t>Red Tower Books (Entangled Publishing)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
-        </is>
+          <t>02/05/2023</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3306,27 +3270,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Every Summer After</t>
+          <t>House of Sky and Breath (1 of 2) [Dramatized Adaptation]: Crescent City 2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carley Fortune</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10/05/2022</t>
+          <t>15/02/2022</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -3339,17 +3303,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Romance Revival</t>
+          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Christina Lauren</t>
+          <t>Taylor Jenkins Reid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gallery Books</t>
+          <t>Atria Books</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3359,8 +3323,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
-        </is>
+          <t>13/06/2017</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -3369,27 +3336,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Seven Husbands of Evelyn Hugo: A Novel</t>
+          <t>Caught Up</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taylor Jenkins Reid</t>
+          <t>Navessa Allen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Zando – Slowburn</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13/06/2017</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3402,28 +3369,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>This Story Might Save Your Life: A Novel</t>
+          <t>A Court of Thorns and Roses (1 of 2) [Dramatized Adaptation]: A Court of Thorns and Roses 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tiffany Crum</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Flatiron Books: Pine &amp; Cedar</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
-        </is>
+          <t>05/05/2015</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -3432,28 +3402,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Into the Blue: Reese's Book Club: A Love Story</t>
+          <t>A Court of Mist and Fury (1 of 2) [Dramatized Adaptation]: A Court of Thorns and Roses 2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Emma Brodie</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ballantine Books</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
-        </is>
+          <t>03/05/2016</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -3462,27 +3435,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caught Up</t>
+          <t>House of Flame and Shadow (1 of 2) [Dramatized Adaptation]: Crescent City 3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Navessa Allen</t>
+          <t>Sarah J. Maas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zando</t>
+          <t>Bloomsbury Publishing</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>30/01/2024</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3495,27 +3468,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Love Hypothesis</t>
+          <t>Fourth Wing (2 of 2) [Dramatized Adaptation]: The Empyrean 1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ali Hazelwood</t>
+          <t>Rebecca Yarros</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Berkley Books</t>
+          <t>GraphicAudio</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14/09/2021</t>
+          <t>09/02/2024</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3588,27 +3561,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dear Debbie</t>
+          <t>Mad Mabel: A Novel</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Freida McFadden</t>
+          <t>Sally Hepworth</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Poisoned Pen Press</t>
+          <t>St. Martin's Press</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Macmillan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
     </row>
@@ -3618,27 +3591,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mad Mabel: A Novel</t>
+          <t>The Divorce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sally Hepworth</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>St. Martin's Press</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
     </row>
@@ -3648,28 +3621,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>It Could Have Been Her: A Novel</t>
+          <t>The Silent Patient</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lisa Jewell</t>
+          <t>Alex Michaelides</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Atria Books</t>
+          <t>Celadon Books</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
-        </is>
+          <t>05/02/2019</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3678,17 +3654,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nobody Knows You're Here: A Psychological Suspense Thriller</t>
+          <t>The Mad Wife</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bryn Greenwood</t>
+          <t>Meagan Church</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Podium Publishing</t>
+          <t>Sourcebooks Landmark</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3698,8 +3674,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
-        </is>
+          <t>30/09/2025</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -3708,17 +3687,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Mad Wife</t>
+          <t>Dear Debbie</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meagan Church</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sourcebooks Landmark</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3728,7 +3707,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
     </row>
@@ -3738,31 +3717,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Silent Patient</t>
+          <t>Murder at the Grand Alpine Hotel: The New Miss Marple Mystery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alex Michaelides</t>
+          <t>Lucy Foley, Agatha Christie</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Celadon Books</t>
+          <t>William Morrow</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/02/2019</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
+          <t>22/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -3771,27 +3747,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Guilty Ones: A Psychological Thriller</t>
+          <t>The Unknown: A Novel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kyla Stone</t>
+          <t>Riley Sager</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paper Moon Press</t>
+          <t>Dutton</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
     </row>
@@ -3801,17 +3777,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Asylum Confessions: Deathbed Confessions of the Criminally Insane</t>
+          <t>Brain Damage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jack Steen</t>
+          <t>Freida McFadden</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deathbed Publishing</t>
+          <t>Hollywood Upstairs Publishing</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3821,7 +3797,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2021</t>
+          <t>28/04/2016</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3834,17 +3810,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Incidents Around the House: A Novel: The Inspiration for the Movie "Other Mommy"</t>
+          <t>Exit Party: A Novel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Josh Malerman</t>
+          <t>Emily St. John Mandel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Del Rey</t>
+          <t>Alfred A. Knopf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3854,11 +3830,8 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25/06/2024</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
+          <t>15/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3867,7 +3840,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Housemaid: An absolutely addictive psychological thriller with a jaw-dropping twist</t>
+          <t>The Boyfriend: A Psychological Thriller</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3877,17 +3850,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bookouture</t>
+          <t>Poisoned Pen Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01/04/2022</t>
+          <t>01/10/2024</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3970,7 +3943,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Scholastic</t>
+          <t>Scholastic Corporation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4059,27 +4032,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
+          <t>Harry Potter and the Goblet of Fire</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rick Riordan</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Miramax Books</t>
+          <t>Bloomsbury, Scholastic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>28/06/2005</t>
+          <t>08/07/2000</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4092,27 +4065,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
+          <t>Harry Potter and the Philosopher's Stone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Arnold Lobel</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>02/11/2004</t>
+          <t>26/06/1997</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4125,17 +4098,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Disney*Pixar Storybook Collection</t>
+          <t>The Lightning Thief: Percy Jackson and the Olympians: Book 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>Rick Riordan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Disney Press</t>
+          <t>Miramax Books</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4145,7 +4118,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/2006</t>
+          <t>28/06/2005</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4158,31 +4131,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Lion, the Witch and the Wardrobe: Classic Fantasy Tale for Kids</t>
+          <t>Frog and Toad Audio Collection: A Box Set of 3 Books From the Classic Animal Friendship and Adventure Series for Kids [ages 4-8] – A Heartwarming Caldecott and Newbery Honor Collection</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C. S. Lewis</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Geoffrey Bles</t>
+          <t>Arnold Lobel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>16/10/1950</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4191,27 +4151,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Little House in the Big Woods</t>
+          <t>Harry Potter and the Chamber of Secrets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Laura Ingalls Wilder</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Harper &amp; Brothers</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/1932</t>
+          <t>02/07/1998</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4224,27 +4184,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Boxcar Children Collection Volume 1: The Boxcar Children, Surprise Island, Yellow House Mystery</t>
+          <t>Harry Potter and the Prisoner of Azkaban</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gertrude Chandler Warner</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rand McNally</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1924</t>
+          <t>08/07/1999</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4257,17 +4217,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spider-Man Storybook Collection</t>
+          <t>Bluey: The Beach and Other Stories</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Marvel Press</t>
+          <t>Penguin Young Readers Licenses</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Marvel Press</t>
+          <t>Listening Library</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4277,11 +4237,8 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>03/05/2016</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
+          <t>01/09/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4350,27 +4307,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
+          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jonathan Haidt</t>
+          <t>Lindsay C. Gibson PsyD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Penguin Press</t>
+          <t>New Harbinger Publications</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26/03/2024</t>
+          <t>01/06/2015</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4383,27 +4340,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adult Children of Emotionally Immature Parents: How to Heal from Distant, Rejecting, or Self-Involved Parents</t>
+          <t>The Anxious Generation: How the Great Rewiring of Childhood Is Causing an Epidemic of Mental Illness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lindsay C. Gibson PsyD</t>
+          <t>Jonathan Haidt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>New Harbinger Publications</t>
+          <t>Penguin Press</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/06/2015</t>
+          <t>26/03/2024</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -4416,27 +4373,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
+          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Michaeleen Doucleff</t>
+          <t>Becky Kennedy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Avid Reader Press/Simon &amp; Schuster</t>
+          <t>Harper Wave</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01/01/2021</t>
+          <t>13/09/2022</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -4449,17 +4406,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Good Inside: A Practical Guide to Resilient Parenting Prioritizing Connection Over Correction</t>
+          <t>The Simple Guide to ADHD Regulation: The Secret to Finding Balance, Getting Things Done, and Enjoying Your Life</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Becky Kennedy</t>
+          <t>Jenna Free, CCC</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Harper Wave</t>
+          <t>Harper Celebrate</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4469,11 +4426,8 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>13/09/2022</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
+          <t>17/03/2026</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -4482,27 +4436,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
+          <t>Hunt, Gather, Parent: What Ancient Cultures Can Teach Us About the Lost Art of Raising Happy, Helpful Little Humans</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Emily Oster</t>
+          <t>Michaeleen Doucleff</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The Penguin Press</t>
+          <t>Avid Reader Press/Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01/01/2013</t>
+          <t>08/03/2022</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4515,17 +4469,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
+          <t>Let's F*cking Date: Become the Prize, Enjoy the Ride, and Never Settle Again</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>John M. Gottman PhD, Nan Silver</t>
+          <t>Serena Kerrigan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Crown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4499,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cribsheet: A Data-Driven Guide to Better, More Relaxed Parenting, from Birth to Preschool</t>
+          <t>Expecting Better: Why the Conventional Pregnancy Wisdom Is Wrong--and What You Really Need to Know</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4545,17 +4509,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Penguin Press</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Penguin Random House</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Penguin Random House</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>09/04/2019</t>
+          <t>20/08/2013</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4568,28 +4532,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>REBUILD: The Complete Guide to Starting Over as a Man</t>
+          <t>The Seven Principles for Making Marriage Work: A Practical Guide from the Country’s Foremost Relationship Expert, Revised and Updated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ralph Brewer</t>
+          <t>John M. Gottman PhD, Nan Silver</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Help For Men</t>
+          <t>Harmony</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
-        </is>
+          <t>01/01/1999</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4598,31 +4565,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>It's Not You: Identifying and Healing from Narcissistic People</t>
+          <t>The Trauma Your Body Never Forgot: How Childhood Abuse, Neglect, and Violence Rewire Your Brain, Your Health, and Your Relationships. And How to Finally Heal.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ramani Durvasula PhD</t>
+          <t>Marieme Seck</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The Open Field</t>
+          <t>Storytel International</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>20/02/2024</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4631,27 +4590,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mating in Captivity: In Search of Erotic Intelligence</t>
+          <t>Men with Adult ADHD: How to Raise Emotionally Intelligent Men and Improve Relationships</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Esther Perel</t>
+          <t>Garth Zeus</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Garth Zeus</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/09/2006</t>
+          <t>01/01/2023</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4724,31 +4683,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mythos</t>
+          <t>Swan Song: Diana, my sister</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
+          <t>Charles Spencer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Michael Joseph</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+          <t>22/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4767,7 +4723,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Signal</t>
+          <t>Dvir Publishing House Ltd.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4777,7 +4733,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>28/10/2014</t>
+          <t>01/01/2011</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -4790,31 +4746,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Odyssey: The Greek Myths Reimagined</t>
+          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Stephen Fry</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Michael Joseph</t>
+          <t>Andrew Ross Sorkin</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>01/01/2024</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -4823,27 +4766,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Third Reich: A History of Nazi Germany</t>
+          <t>Project MK-Ultra: The History of the CIA’s Controversial Human Experimentation Program</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thomas Childers</t>
+          <t>Charles River Editors</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Charles River Editors</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/01/2017</t>
+          <t>21/06/2022</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4856,27 +4799,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nuclear War: A Scenario</t>
+          <t>Mythos</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annie Jacobsen</t>
+          <t>Stephen Fry</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dutton</t>
+          <t>Michael Joseph</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>26/03/2024</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4889,27 +4832,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A People's History of the United States</t>
+          <t>Nuclear War: A Scenario</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Howard Zinn</t>
+          <t>Annie Jacobsen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Harper &amp; Row</t>
+          <t>Dutton</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/1980</t>
+          <t>26/03/2024</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4922,28 +4865,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1929: Inside the Greatest Crash in Wall Street History--and How It Shattered a Nation</t>
+          <t>Empire of the Summer Moon: Quanah Parker and the Rise and Fall of the Comanches, the Most Powerful Indian Tribe in American History</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Andrew Ross Sorkin</t>
+          <t>S. C. Gwynne</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Viking Press</t>
+          <t>Scribner</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
-        </is>
+          <t>25/05/2010</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4952,27 +4898,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Christian History: An Enthralling Guide to the Story of Christianity, From Its Early Origins Through the Crusades and Knights Templar to Modern Times</t>
+          <t>A People's History of the United States</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Billy Wellman, Enthralling History</t>
+          <t>Howard Zinn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Billy Wellman</t>
+          <t>Harper &amp; Row</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Independent</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>01/01/1980</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4985,27 +4931,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Power Broker: Robert Moses and the Fall of New York</t>
+          <t>The Only Plane in the Sky (Revised and Expanded Edition for the 25th Anniversary): An Oral History of September 11, 2001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Robert A. Caro</t>
+          <t>Garrett M. Graff, Holter Graham</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Alfred A. Knopf</t>
+          <t>Avid Reader Press</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Penguin Random House</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01/01/1974</t>
+          <t>10/09/2019</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5018,17 +4964,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Codename Nemo: The Hunt for a Nazi U-Boat and the Elusive Enigma Machine</t>
+          <t>The Gales of November: The Untold Story of the Edmund Fitzgerald</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charles Lachman</t>
+          <t>John U. Bacon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diversion Books</t>
+          <t>Liveright Publishing Corporation</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5038,7 +4984,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>04/06/2024</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -5144,17 +5090,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Become What You Are</t>
+          <t>The King James Bible</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alan Watts</t>
+          <t>Uncredited</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Shambhala</t>
+          <t>Robert Barker</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5164,7 +5110,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01/07/1995</t>
+          <t>01/01/1611</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -5177,17 +5123,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The King James Bible</t>
+          <t>Become What You Are</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uncredited</t>
+          <t>Alan Watts</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Robert Barker</t>
+          <t>Shambhala</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5197,7 +5143,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>02/05/1611</t>
+          <t>01/01/1995</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -5210,27 +5156,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A Life of Meaning: Exploring Our Deepest Questions and Motivations</t>
+          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>James Hollis PhD</t>
+          <t>Paulo Coelho</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Macmillan Audio</t>
+          <t>HarperOne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>HarperCollins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01/12/2020</t>
+          <t>01/11/2010</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5243,31 +5189,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Alchemist: A Modern Classic Fable of Spiritual Healing, Self-Discovery, and the Power of Dreams in a Visually Stunning Graphic Novel—Get Lost in the Pages of This Captivating Summer Read</t>
+          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Paulo Coelho</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>HarperOne</t>
+          <t>Zondervan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>01/11/2010</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>Independent</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5276,27 +5209,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NIV Listener's Audio Bible: Complete Bible: Vocal Performance by Max McLean</t>
+          <t>Mere Christianity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>C. S. Lewis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Zondervan</t>
+          <t>Geoffrey Bles</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HarperCollins</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01/01/2015</t>
+          <t>07/07/1952</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -5342,12 +5275,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Book of Enoch</t>
+          <t>Becoming Supernatural: How Common People Are Doing The Uncommon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>George Schodde</t>
+          <t>Dr. Joe Dispenza</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Hay House Inc.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5357,7 +5295,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>01/01/1882</t>
+          <t>01/01/2017</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5370,31 +5308,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Becoming Supernatural: How Common People Are Doing The Uncommon</t>
+          <t>Shaolin Spirit: The Way to Self-Mastery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dr. Joe Dispenza</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Hay House LLC</t>
+          <t>Shi Heng Yi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Independent</t>
         </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>31/10/2017</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -5403,28 +5328,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stand Firm and Act Like Men: Becoming the Man You Were Created to Be Instead of Who the World Says You Are</t>
+          <t>When God Was a Woman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Joby Martin, Charles Martin</t>
+          <t>Merlin Stone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faithwords</t>
+          <t>Dial Press</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Penguin Random House</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
-        </is>
+          <t>01/01/1976</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5438,7 +5366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5493,17 +5421,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A Court of Thorns and Roses</t>
+          <t>Harry Potter and the Order of the Phoenix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>J.K. Rowling</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Bloomsbury</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5513,7 +5441,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>05/05/2015</t>
+          <t>21/06/2003</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5526,27 +5454,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A Court of Mist and Fury</t>
+          <t>Twilight</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sarah J. Maas</t>
+          <t>Stephenie Meyer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bloomsbury Publishing</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>03/05/2016</t>
+          <t>05/10/2005</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -5559,7 +5487,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Harry Potter and the Goblet of Fire</t>
+          <t>Harry Potter and the Half-Blood Prince</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5579,7 +5507,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>08/07/2000</t>
+          <t>16/07/2005</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -5592,7 +5520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Harry Potter and the Order of the Phoenix</t>
+          <t>Harry Potter and the Deathly Hallows</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5602,17 +5530,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Bloomsbury Publishing (UK), Scholastic (US), Raincoast Books (Canada)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Bloomsbury</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bloomsbury</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21/06/2003</t>
+          <t>21/07/2007</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -5625,31 +5553,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Twilight</t>
+          <t>Trust Fall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Lynn Painter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Simon &amp; Schuster Books for Young Readers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/10/2005</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
+          <t>29/09/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5658,27 +5583,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Summer I Turned Pretty</t>
+          <t>Midnight Sun</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jenny Han</t>
+          <t>Stephenie Meyer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster Books for Young Readers</t>
+          <t>Little, Brown and Company</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Simon &amp; Schuster</t>
+          <t>Hachette</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/05/2009</t>
+          <t>04/08/2020</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -5691,27 +5616,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Children of Blood and Bone</t>
+          <t>Lord of the Flies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tomi Adeyemi</t>
+          <t>William Golding</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Henry Holt Books for Young Readers</t>
+          <t>Faber and Faber</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Macmillan</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>06/03/2018</t>
+          <t>17/09/1954</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -5724,27 +5649,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Midnight Sun</t>
+          <t>Eragon: Inheritance, Book I</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Stephenie Meyer</t>
+          <t>Christopher Paolini</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Little, Brown and Company</t>
+          <t>Paolini LLC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hachette</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>04/08/2020</t>
+          <t>01/01/2002</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -5757,31 +5682,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Harry Potter and the Half-Blood Prince</t>
+          <t>Better Than the Movies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>J.K. Rowling</t>
+          <t>Lynn Painter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bloomsbury (UK) / Scholastic (US)</t>
+          <t>Simon &amp; Schuster Books for Young Readers</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bloomsbury</t>
+          <t>Simon &amp; Schuster</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16/07/2005</t>
+          <t>04/05/2021</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>True Paranormal Stories: 10 Real Encounters You'll Never Forget</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Scary Studios</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Scary Studios</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>19/07/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
